--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250328120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-28T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>RESP_OFFRE_STRUCT</t>
   </si>
   <si>
-    <t>Responsable Offre de structure</t>
+    <t>Responsable de structure</t>
   </si>
   <si>
     <t>RESP_DISPO_PLACE</t>
